--- a/Статистика по рейсам Шестаков А.Ю. ЕТ-112.xlsx
+++ b/Статистика по рейсам Шестаков А.Ю. ЕТ-112.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10830"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6292EDC4-EED5-C74E-AB05-B0A5F36081F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B0FB6C-0E99-4E47-AA35-ABB70D7777AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -493,7 +493,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -594,9 +594,7 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
@@ -604,9 +602,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -6543,19 +6538,19 @@
       <c r="C1" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="I1" s="46" t="s">
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="I1" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="18">
@@ -6576,18 +6571,18 @@
       <c r="G2" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="42" t="s">
+      <c r="I2" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42" t="s">
+      <c r="J2" s="40"/>
+      <c r="K2" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42" t="s">
+      <c r="L2" s="40"/>
+      <c r="M2" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="42"/>
+      <c r="N2" s="40"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="21">
@@ -6611,22 +6606,22 @@
         <f>MEDIAN(C2:C224)</f>
         <v>27.8</v>
       </c>
-      <c r="I3" s="40" t="s">
+      <c r="I3" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="40">
+      <c r="J3">
         <v>31.682152466367707</v>
       </c>
-      <c r="K3" s="40" t="s">
+      <c r="K3" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="40">
+      <c r="L3">
         <v>70.50910313901349</v>
       </c>
-      <c r="M3" s="40" t="s">
+      <c r="M3" t="s">
         <v>28</v>
       </c>
-      <c r="N3" s="40">
+      <c r="N3">
         <v>27.71704035874442</v>
       </c>
     </row>
@@ -6649,22 +6644,22 @@
       <c r="G4" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="40" t="s">
+      <c r="I4" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="40">
+      <c r="J4">
         <v>0.31881932733054769</v>
       </c>
-      <c r="K4" s="40" t="s">
+      <c r="K4" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="40">
+      <c r="L4">
         <v>0.25828748160394982</v>
       </c>
-      <c r="M4" s="40" t="s">
+      <c r="M4" t="s">
         <v>29</v>
       </c>
-      <c r="N4" s="40">
+      <c r="N4">
         <v>0.18243576147935742</v>
       </c>
     </row>
@@ -6690,22 +6685,22 @@
         <f>AVERAGE(C2:C224)</f>
         <v>27.71704035874442</v>
       </c>
-      <c r="I5" s="40" t="s">
+      <c r="I5" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5">
         <v>33.29</v>
       </c>
-      <c r="K5" s="40" t="s">
+      <c r="K5" t="s">
         <v>30</v>
       </c>
-      <c r="L5" s="40">
+      <c r="L5">
         <v>70.7</v>
       </c>
-      <c r="M5" s="40" t="s">
+      <c r="M5" t="s">
         <v>30</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5">
         <v>27.8</v>
       </c>
     </row>
@@ -6728,22 +6723,22 @@
       <c r="G6" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="40" t="s">
+      <c r="I6" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="40">
+      <c r="J6">
         <v>37</v>
       </c>
-      <c r="K6" s="40" t="s">
+      <c r="K6" t="s">
         <v>31</v>
       </c>
-      <c r="L6" s="40">
+      <c r="L6">
         <v>73.599999999999994</v>
       </c>
-      <c r="M6" s="40" t="s">
+      <c r="M6" t="s">
         <v>31</v>
       </c>
-      <c r="N6" s="40">
+      <c r="N6">
         <v>26.03</v>
       </c>
     </row>
@@ -6769,22 +6764,22 @@
         <f>_xlfn.VAR.S(C2:C224)</f>
         <v>7.4220659758413179</v>
       </c>
-      <c r="I7" s="40" t="s">
+      <c r="I7" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="40">
+      <c r="J7">
         <v>4.7609878445475102</v>
       </c>
-      <c r="K7" s="40" t="s">
+      <c r="K7" t="s">
         <v>32</v>
       </c>
-      <c r="L7" s="40">
+      <c r="L7">
         <v>3.8570546227903342</v>
       </c>
-      <c r="M7" s="40" t="s">
+      <c r="M7" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="40">
+      <c r="N7">
         <v>2.7243468897776797</v>
       </c>
     </row>
@@ -6807,22 +6802,22 @@
       <c r="G8" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="I8" s="40" t="s">
+      <c r="I8" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="40">
+      <c r="J8">
         <v>22.667005255929144</v>
       </c>
-      <c r="K8" s="40" t="s">
+      <c r="K8" t="s">
         <v>33</v>
       </c>
-      <c r="L8" s="40">
+      <c r="L8">
         <v>14.876870363188289</v>
       </c>
-      <c r="M8" s="40" t="s">
+      <c r="M8" t="s">
         <v>33</v>
       </c>
-      <c r="N8" s="40">
+      <c r="N8">
         <v>7.4220659758413179</v>
       </c>
     </row>
@@ -6848,22 +6843,22 @@
         <f t="shared" si="0"/>
         <v>26.03</v>
       </c>
-      <c r="I9" s="40" t="s">
+      <c r="I9" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="40">
+      <c r="J9">
         <v>-0.45259084438104935</v>
       </c>
-      <c r="K9" s="40" t="s">
+      <c r="K9" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="40">
+      <c r="L9">
         <v>0.80913590853790529</v>
       </c>
-      <c r="M9" s="40" t="s">
+      <c r="M9" t="s">
         <v>34</v>
       </c>
-      <c r="N9" s="40">
+      <c r="N9">
         <v>-0.59378118882805486</v>
       </c>
     </row>
@@ -6877,31 +6872,31 @@
       <c r="C10" s="27">
         <v>24.26</v>
       </c>
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="43" t="s">
+      <c r="F10" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="43" t="s">
+      <c r="G10" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="I10" s="40" t="s">
+      <c r="I10" t="s">
         <v>35</v>
       </c>
-      <c r="J10" s="40">
+      <c r="J10">
         <v>-0.76253261087973223</v>
       </c>
-      <c r="K10" s="40" t="s">
+      <c r="K10" t="s">
         <v>35</v>
       </c>
-      <c r="L10" s="40">
+      <c r="L10">
         <v>-0.57603286438894197</v>
       </c>
-      <c r="M10" s="40" t="s">
+      <c r="M10" t="s">
         <v>35</v>
       </c>
-      <c r="N10" s="40">
+      <c r="N10">
         <v>-2.2805180099050803E-3</v>
       </c>
     </row>
@@ -6927,22 +6922,22 @@
         <f t="shared" si="1"/>
         <v>2.7243468897776797</v>
       </c>
-      <c r="I11" s="40" t="s">
+      <c r="I11" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="40">
+      <c r="J11">
         <v>20.25</v>
       </c>
-      <c r="K11" s="40" t="s">
+      <c r="K11" t="s">
         <v>36</v>
       </c>
-      <c r="L11" s="40">
+      <c r="L11">
         <v>23.850000000000009</v>
       </c>
-      <c r="M11" s="40" t="s">
+      <c r="M11" t="s">
         <v>36</v>
       </c>
-      <c r="N11" s="40">
+      <c r="N11">
         <v>12.720000000000002</v>
       </c>
     </row>
@@ -6956,22 +6951,22 @@
       <c r="C12" s="22">
         <v>24.86</v>
       </c>
-      <c r="I12" s="40" t="s">
+      <c r="I12" t="s">
         <v>37</v>
       </c>
-      <c r="J12" s="40">
+      <c r="J12">
         <v>19.75</v>
       </c>
-      <c r="K12" s="40" t="s">
+      <c r="K12" t="s">
         <v>37</v>
       </c>
-      <c r="L12" s="40">
+      <c r="L12">
         <v>56.55</v>
       </c>
-      <c r="M12" s="40" t="s">
+      <c r="M12" t="s">
         <v>37</v>
       </c>
-      <c r="N12" s="40">
+      <c r="N12">
         <v>21.87</v>
       </c>
     </row>
@@ -6985,22 +6980,22 @@
       <c r="C13" s="30">
         <v>22.3</v>
       </c>
-      <c r="I13" s="40" t="s">
+      <c r="I13" t="s">
         <v>38</v>
       </c>
-      <c r="J13" s="40">
+      <c r="J13">
         <v>40</v>
       </c>
-      <c r="K13" s="40" t="s">
+      <c r="K13" t="s">
         <v>38</v>
       </c>
-      <c r="L13" s="40">
+      <c r="L13">
         <v>80.400000000000006</v>
       </c>
-      <c r="M13" s="40" t="s">
+      <c r="M13" t="s">
         <v>38</v>
       </c>
-      <c r="N13" s="40">
+      <c r="N13">
         <v>34.590000000000003</v>
       </c>
     </row>
@@ -7014,22 +7009,22 @@
       <c r="C14" s="20">
         <v>23.19</v>
       </c>
-      <c r="I14" s="40" t="s">
+      <c r="I14" t="s">
         <v>39</v>
       </c>
-      <c r="J14" s="40">
+      <c r="J14">
         <v>7065.119999999999</v>
       </c>
-      <c r="K14" s="40" t="s">
+      <c r="K14" t="s">
         <v>39</v>
       </c>
-      <c r="L14" s="40">
+      <c r="L14">
         <v>15723.530000000008</v>
       </c>
-      <c r="M14" s="40" t="s">
+      <c r="M14" t="s">
         <v>39</v>
       </c>
-      <c r="N14" s="40">
+      <c r="N14">
         <v>6180.900000000006</v>
       </c>
     </row>
@@ -7043,22 +7038,22 @@
       <c r="C15" s="22">
         <v>23.9</v>
       </c>
-      <c r="I15" s="40" t="s">
+      <c r="I15" t="s">
         <v>40</v>
       </c>
-      <c r="J15" s="40">
+      <c r="J15">
         <v>223</v>
       </c>
-      <c r="K15" s="40" t="s">
+      <c r="K15" t="s">
         <v>40</v>
       </c>
-      <c r="L15" s="40">
+      <c r="L15">
         <v>223</v>
       </c>
-      <c r="M15" s="40" t="s">
+      <c r="M15" t="s">
         <v>40</v>
       </c>
-      <c r="N15" s="40">
+      <c r="N15">
         <v>223</v>
       </c>
     </row>
@@ -7072,22 +7067,22 @@
       <c r="C16" s="20">
         <v>22.18</v>
       </c>
-      <c r="I16" s="40" t="s">
+      <c r="I16" t="s">
         <v>41</v>
       </c>
-      <c r="J16" s="40">
+      <c r="J16">
         <v>40</v>
       </c>
-      <c r="K16" s="40" t="s">
+      <c r="K16" t="s">
         <v>41</v>
       </c>
-      <c r="L16" s="40">
+      <c r="L16">
         <v>80.400000000000006</v>
       </c>
-      <c r="M16" s="40" t="s">
+      <c r="M16" t="s">
         <v>41</v>
       </c>
-      <c r="N16" s="40">
+      <c r="N16">
         <v>34.590000000000003</v>
       </c>
     </row>
@@ -7101,22 +7096,22 @@
       <c r="C17" s="22">
         <v>23.19</v>
       </c>
-      <c r="I17" s="40" t="s">
+      <c r="I17" t="s">
         <v>42</v>
       </c>
-      <c r="J17" s="40">
+      <c r="J17">
         <v>19.75</v>
       </c>
-      <c r="K17" s="40" t="s">
+      <c r="K17" t="s">
         <v>42</v>
       </c>
-      <c r="L17" s="40">
+      <c r="L17">
         <v>56.55</v>
       </c>
-      <c r="M17" s="40" t="s">
+      <c r="M17" t="s">
         <v>42</v>
       </c>
-      <c r="N17" s="40">
+      <c r="N17">
         <v>21.87</v>
       </c>
     </row>
@@ -7130,22 +7125,22 @@
       <c r="C18" s="27">
         <v>23.77</v>
       </c>
-      <c r="I18" s="41" t="s">
+      <c r="I18" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="J18" s="41">
+      <c r="J18" s="32">
         <v>0.62829960614138169</v>
       </c>
-      <c r="K18" s="41" t="s">
+      <c r="K18" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="L18" s="41">
+      <c r="L18" s="32">
         <v>0.50900905011558251</v>
       </c>
-      <c r="M18" s="41" t="s">
+      <c r="M18" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="N18" s="41">
+      <c r="N18" s="32">
         <v>0.35952750431827596</v>
       </c>
     </row>
